--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/dmpCfgInputDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/dmpCfgInputDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25230" windowHeight="11355"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="中台拉取任务表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>输入信息id</t>
   </si>
@@ -68,6 +68,9 @@
     <t>任务类型</t>
   </si>
   <si>
+    <t>最大间隔时间(秒)</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -120,6 +123,12 @@
   </si>
   <si>
     <t>{.taskTypeName}</t>
+  </si>
+  <si>
+    <t>{.maxIntervalTime}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1324,13 +1333,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="18" width="30" customWidth="1"/>
+    <col min="1" max="19" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:20">
+    <row r="1" ht="15" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1385,64 +1394,70 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
